--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N48_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N48_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>27.57291941570015</v>
+        <v>4.480599405051275</v>
       </c>
       <c r="D2" t="n">
-        <v>28.23877369033315</v>
+        <v>4.588800724679136</v>
       </c>
       <c r="E2" t="n">
-        <v>14.08468082401629</v>
+        <v>2.288760633902647</v>
       </c>
       <c r="F2" t="n">
-        <v>6.471774597971961</v>
+        <v>1.051663372170444</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.29923548954151</v>
+        <v>5.898625767050495</v>
       </c>
       <c r="D3" t="n">
-        <v>35.05970181166774</v>
+        <v>5.697201544396007</v>
       </c>
       <c r="E3" t="n">
-        <v>14.08468082401629</v>
+        <v>2.288760633902647</v>
       </c>
       <c r="F3" t="n">
-        <v>6.471774597971961</v>
+        <v>1.051663372170444</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>5.650443414967659</v>
+        <v>0.9181970549322447</v>
       </c>
       <c r="D4" t="n">
-        <v>17.08930755650705</v>
+        <v>2.777012477932396</v>
       </c>
       <c r="E4" t="n">
-        <v>14.08468082401629</v>
+        <v>2.288760633902647</v>
       </c>
       <c r="F4" t="n">
-        <v>6.471774597971961</v>
+        <v>1.051663372170444</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.173821110011</v>
+        <v>5.390745930376787</v>
       </c>
       <c r="D5" t="n">
-        <v>19.21358181630052</v>
+        <v>3.122207045148834</v>
       </c>
       <c r="E5" t="n">
-        <v>14.08468082401629</v>
+        <v>2.288760633902647</v>
       </c>
       <c r="F5" t="n">
-        <v>6.471774597971961</v>
+        <v>1.051663372170444</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>38.69310395997899</v>
+        <v>6.287629393496586</v>
       </c>
       <c r="D6" t="n">
-        <v>24.12342216935723</v>
+        <v>3.92005610252055</v>
       </c>
       <c r="E6" t="n">
-        <v>14.08468082401629</v>
+        <v>2.288760633902647</v>
       </c>
       <c r="F6" t="n">
-        <v>6.471774597971961</v>
+        <v>1.051663372170444</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>52.30244898445186</v>
+        <v>8.499147959973428</v>
       </c>
       <c r="D7" t="n">
-        <v>31.93754506970058</v>
+        <v>5.189851073826345</v>
       </c>
       <c r="E7" t="n">
-        <v>14.08468082401629</v>
+        <v>2.288760633902647</v>
       </c>
       <c r="F7" t="n">
-        <v>6.471774597971961</v>
+        <v>1.051663372170444</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
